--- a/발송대상_본부별_정리.xlsx
+++ b/발송대상_본부별_정리.xlsx
@@ -1985,10 +1985,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">김민석 대리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02-517-4055 / 010-686-5344</t>
+    <t xml:space="preserve">영업팀 김민석 과장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-517-4055 / 010-6286-5344</t>
   </si>
   <si>
     <r>
@@ -2050,16 +2050,50 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">김민석 대리 연락처 자릿수 확인 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(010-686-5344)</t>
+      <t xml:space="preserve">담당자 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연락처 수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기존 김민석 대리 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">010-686-5344)</t>
     </r>
   </si>
   <si>
@@ -2184,20 +2218,53 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">충청남도 천안시 동남구 동면 수남리 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">157-1</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">지번 주소 — 도로명 주소 확인 필요</t>
+      <t xml:space="preserve">충남 천안시 동남구 동면 화복로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">292</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도로명 주소로 수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기존 지번 ‘동면 수남리 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">157-1’)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">주식회사 씨엔에프</t>
@@ -2356,7 +2423,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">전라남도 해남군 마산면 식품늑화당지길</t>
+      <t xml:space="preserve">전남광주 해남군 마산면 식품특화단지길 </t>
     </r>
     <r>
       <rPr>
@@ -2375,33 +2442,33 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">도로명 확인 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(‘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">식품늑화당지길’ 표기 오류 가능</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">주소 수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기존 ‘전라남도 해남군 마산면 식품늑화당지길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">82’)</t>
     </r>
   </si>
   <si>
@@ -6067,7 +6134,7 @@
       </c>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="n">
         <v>23</v>
       </c>
@@ -8054,7 +8121,7 @@
       <c r="I42" s="12"/>
       <c r="J42" s="13"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="n">
         <v>40</v>
       </c>
@@ -10247,7 +10314,7 @@
       </c>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="n">
         <v>17</v>
       </c>
